--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="musk" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="16.77734375" customWidth="1"/>
@@ -600,6 +600,14 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="32.4">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="musk" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -138,16 +138,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"A":"殺死半獸人",
-"B":["接受/quest karen_01","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"...",
-"B":["任務完成了/goto none;close karen_01;set quest none"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"A":"你好...",
 "B":["交易/trade","(#quest!=none)任務/goto #quest:melanie_01","離開/exit"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -191,14 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>karen_01_open</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>karen_01_finish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>:trump_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -224,6 +206,24 @@
   </si>
   <si>
     <t>musk_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"找尋失落的劍",
+"B":["接受/quest karen_01","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"type":"quest",
+"start":{
+"A":"找尋失落的劍",
+"B":["接受/quest karen_01","離開/exit"]},
+"open":{
+"A":"...",
+"B":["離開/exit"]},
+"report":{
+"A":"...",
+"B":["任務完成了/goto none;close karen_01;set quest none"]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,7 +596,7 @@
     </row>
     <row r="3" spans="1:2" ht="162">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>16</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -723,7 +723,7 @@
     </row>
     <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>17</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>20</v>
@@ -809,7 +809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -834,33 +834,25 @@
     </row>
     <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="32.4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="162">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="32.4">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -892,20 +884,20 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -913,10 +905,10 @@
     </row>
     <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="32.4">

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="musk" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,12 +101,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"A":"你好
-我是行商…想要買什麼?",
-"B":["交易/trade","(#quest!=none)任務/goto #quest:macron_01","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"A":"殺死半獸人",
 "B":["接受/quest macron_01","離開/exit"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,11 +128,6 @@
   </si>
   <si>
     <t>"A":"你好...",
-"B":["交易/trade","(#quest!=none)任務/goto #quest:karen_01","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"你好...",
 "B":["交易/trade","(#quest!=none)任務/goto #quest:melanie_01","離開/exit"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -209,21 +198,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>top1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"你好",
+"B":["交易/trade","[opt]","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"你好
+我是行商…想要買什麼?",
+"B":["交易/trade","離開/exit"],
+"cmds":["sete macron top1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"你好...",
+"B":["交易/trade","(#quest!=none)有需要幫助的嗎?/goto #quest:karen_01","[opt]","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>karen_01_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"去問一下馬克宏",
+"B":["離開/goto 0"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>karen_01_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"opt":"Tony在哪裡/goto karen_01_01"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"A":"找尋失落的劍",
-"B":["接受/quest karen_01","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"quest",
-"start":{
-"A":"找尋失落的劍",
-"B":["接受/quest karen_01","離開/exit"]},
-"open":{
-"A":"...",
-"B":["離開/exit"]},
-"report":{
-"A":"...",
-"B":["任務完成了/goto none;close karen_01;set quest none"]}</t>
+"B":["接受/quest karen_01;set quest karen_01_1;add macron karen_01;goto karen_01_1","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"可能躲在小木屋中",
+"B":["交易/trade","[opt]","離開/exit"],
+"cmds":["rm macron karen_01"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,9 +592,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
@@ -586,7 +606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="81">
+    <row r="2" spans="1:2" ht="82.5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -594,15 +614,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="162">
+    <row r="3" spans="1:2" ht="165">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="32.4">
+    <row r="4" spans="1:2" ht="33">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -619,10 +639,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.5546875" customWidth="1"/>
+    <col min="2" max="2" width="63.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -633,7 +653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="64.8">
+    <row r="2" spans="1:2" ht="66">
       <c r="A2">
         <v>0</v>
       </c>
@@ -641,31 +661,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32.4">
+    <row r="3" spans="1:2" ht="33">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="32.4">
+    <row r="4" spans="1:2" ht="33">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32.4">
+    <row r="5" spans="1:2" ht="33">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="32.4">
+    <row r="6" spans="1:2" ht="33">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -682,11 +702,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
-    <col min="2" max="2" width="76.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.75" customWidth="1"/>
+    <col min="2" max="2" width="76.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -697,44 +717,68 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="48.6">
+    <row r="2" spans="1:2" ht="66">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="33">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32.4">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" ht="33">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33">
+      <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="32.4">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="7" spans="1:2" ht="33">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32.4">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="32.4">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="49.5">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -747,10 +791,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="73.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="73.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -761,39 +805,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="48.6">
+    <row r="2" spans="1:2" ht="49.5">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32.4">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="32.4">
+    <row r="4" spans="1:2" ht="33">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32.4">
+    <row r="5" spans="1:2" ht="33">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="32.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -810,10 +854,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="75.44140625" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="85.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -824,31 +868,31 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="32.4">
+    <row r="2" spans="1:2" ht="33">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="32.4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="162">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="33">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="32.4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="33">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -865,10 +909,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="78.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="78.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -879,39 +923,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="32.4">
+    <row r="2" spans="1:2" ht="33">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="33">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32.4">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="32.4">
+    <row r="4" spans="1:2" ht="33">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32.4">
+    <row r="5" spans="1:2" ht="33">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="32.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="33">
       <c r="A6" t="s">
         <v>1</v>
       </c>

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="musk" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>"A":"你好
+我是行商…想要買什麼?",
+"B":["交易/trade","(#quest!=none)任務/goto #quest:macron_01","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"A":"殺死半獸人",
 "B":["接受/quest macron_01","離開/exit"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,6 +134,11 @@
   </si>
   <si>
     <t>"A":"你好...",
+"B":["交易/trade","(#quest!=none)任務/goto #quest:karen_01","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"A":"你好...",
 "B":["交易/trade","(#quest!=none)任務/goto #quest:melanie_01","離開/exit"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -198,52 +209,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>top1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"你好",
-"B":["交易/trade","[opt]","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"你好
-我是行商…想要買什麼?",
-"B":["交易/trade","離開/exit"],
-"cmds":["sete macron top1"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"你好...",
-"B":["交易/trade","(#quest!=none)有需要幫助的嗎?/goto #quest:karen_01","[opt]","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>karen_01_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"去問一下馬克宏",
-"B":["離開/goto 0"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>karen_01_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"opt":"Tony在哪裡/goto karen_01_01"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"A":"找尋失落的劍",
-"B":["接受/quest karen_01;set quest karen_01_1;add macron karen_01;goto karen_01_1","離開/exit"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"A":"可能躲在小木屋中",
-"B":["交易/trade","[opt]","離開/exit"],
-"cmds":["rm macron karen_01"]</t>
+"B":["接受/quest karen_01","離開/exit"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"type":"quest",
+"start":{
+"A":"找尋失落的劍",
+"B":["接受/quest karen_01","離開/exit"]},
+"open":{
+"A":"...",
+"B":["離開/exit"]},
+"report":{
+"A":"...",
+"B":["任務完成了/goto none;close karen_01;set quest none"]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -592,9 +572,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
@@ -606,7 +586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="82.5">
+    <row r="2" spans="1:2" ht="81">
       <c r="A2">
         <v>0</v>
       </c>
@@ -614,15 +594,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="165">
+    <row r="3" spans="1:2" ht="162">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="33">
+    <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -639,10 +619,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="63.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -653,7 +633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="66">
+    <row r="2" spans="1:2" ht="64.8">
       <c r="A2">
         <v>0</v>
       </c>
@@ -661,31 +641,31 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33">
+    <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="33">
+    <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="33">
+    <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="33">
+    <row r="6" spans="1:2" ht="32.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -702,11 +682,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="19.75" customWidth="1"/>
-    <col min="2" max="2" width="76.5" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="2" max="2" width="76.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -717,68 +697,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="66">
+    <row r="2" spans="1:2" ht="48.6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="32.4">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="32.4">
+      <c r="A5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="33">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="33">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
       <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="32.4">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="33">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="33">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="49.5">
-      <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -791,10 +747,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="73.5" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="73.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -805,39 +761,39 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="49.5">
+    <row r="2" spans="1:2" ht="48.6">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="33">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="33">
+    <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="32.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -854,10 +810,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="85.25" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="75.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -868,31 +824,31 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33">
+    <row r="2" spans="1:2" ht="32.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="32.4">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="162">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="33">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="33">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="33">
+    <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -909,10 +865,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="2" max="2" width="78.875" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="78.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -923,39 +879,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="33">
+    <row r="2" spans="1:2" ht="32.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="32.4">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="33">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="32.4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="33">
+    <row r="5" spans="1:2" ht="32.4">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="33">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="32.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -114,7 +114,7 @@
     <t>n_QX01_karen</t>
   </si>
   <si>
-    <t>qx01_pelt_ready</t>
+    <t>item:plet:1</t>
   </si>
   <si>
     <t>離開</t>
@@ -255,7 +255,7 @@
     <t>好的</t>
   </si>
   <si>
-    <t xml:space="preserve">rm qx01_pelt_ready ;
+    <t xml:space="preserve">consume plet 1 ;
 set qx01_karen_done</t>
   </si>
   <si>

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -114,7 +114,7 @@
     <t>n_QX01_karen</t>
   </si>
   <si>
-    <t>item:plet:1</t>
+    <t>item:plet:1 &amp;&amp; !qx01_karen_done</t>
   </si>
   <si>
     <t>離開</t>

--- a/xls/dialog.xlsx
+++ b/xls/dialog.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="karen" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="xi" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="npc_c" state="visible" r:id="rId6"/>
+    <sheet name="karen" sheetId="1" r:id="rId1"/>
+    <sheet name="xi" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -57,7 +56,7 @@
     <t>n_default</t>
   </si>
   <si>
-    <t xml:space="preserve">clr _where;
+    <t>clr _where;
 clr _weapon;
 clr _eat;
 clr _rest</t>
@@ -72,7 +71,7 @@
     <t>node</t>
   </si>
   <si>
-    <t xml:space="preserve">!_first_meet :
+    <t>!_first_meet :
 很高興認識你，我是Karen;
 true :
 你好/需要幫助嗎?</t>
@@ -192,7 +191,7 @@
     <t>接受</t>
   </si>
   <si>
-    <t xml:space="preserve">qstart QK01 ;
+    <t>qstart QK01 ;
 set _quest n_QK01-2</t>
   </si>
   <si>
@@ -211,7 +210,7 @@
     <t>n_QK01-2</t>
   </si>
   <si>
-    <t xml:space="preserve">#QK01==open : 任務如何了? ;
+    <t>#QK01==open : 任務如何了? ;
 #QK01==done : 任務如何了? ;
 #QK01==close : 很好，這是你的獎勵</t>
   </si>
@@ -237,7 +236,7 @@
     <t>#QK01==close</t>
   </si>
   <si>
-    <t xml:space="preserve">choice:
+    <t>choice:
 n_default</t>
   </si>
   <si>
@@ -256,7 +255,7 @@
     <t>好的</t>
   </si>
   <si>
-    <t xml:space="preserve">consume plet 1 ;
+    <t>consume plet 1 ;
 set QX01_s03_done</t>
   </si>
   <si>
@@ -275,7 +274,7 @@
     <t>set QX02_s01_done</t>
   </si>
   <si>
-    <t xml:space="preserve">clr _where ;
+    <t>clr _where ;
 clr _weapon ;
 clr _eat ;
 clr _rest</t>
@@ -284,7 +283,7 @@
     <t>!_first_meet : set _quest n_QX01</t>
   </si>
   <si>
-    <t xml:space="preserve">!_first_meet:
+    <t>!_first_meet:
 很高興認識你，我是Xi;
 true:
 你好/需要幫助嗎?</t>
@@ -305,7 +304,7 @@
     <t>了解</t>
   </si>
   <si>
-    <t xml:space="preserve">rm QK01_s01 ;
+    <t>rm QK01_s01 ;
 set QK01_s01_done</t>
   </si>
   <si>
@@ -315,14 +314,14 @@
     <t>最近黑森林的狼變多了，肉舖都要沒貨了……能幫我獵些狼皮回來嗎？</t>
   </si>
   <si>
-    <t xml:space="preserve">qstart QX01 ;
+    <t>qstart QX01 ;
 set _quest n_QX01-2</t>
   </si>
   <si>
     <t>n_QX01-2</t>
   </si>
   <si>
-    <t xml:space="preserve">#QX01==open : 狼皮收集得如何了? ;
+    <t>#QX01==open : 狼皮收集得如何了? ;
 #QX01==done : 都準備好了嗎？太好了! ;
 #QX01==close : 謝謝你，這是你的獎勵</t>
   </si>
@@ -348,14 +347,14 @@
     <t>森林安靜多了，這下該跟 karen 把長期收購狼皮的事情談攏。你能不能幫我帶個提案去，跟她把價錢跟數量談好？</t>
   </si>
   <si>
-    <t xml:space="preserve">qstart QX02 ;
+    <t>qstart QX02 ;
 set _quest n_QX02-2</t>
   </si>
   <si>
     <t>n_QX02-2</t>
   </si>
   <si>
-    <t xml:space="preserve">#QX02==open : 跟 karen 談得怎麼樣了? ;
+    <t>#QX02==open : 跟 karen 談得怎麼樣了? ;
 #QX02==done : 都談好了嗎？太好了! ;
 #QX02==close : 這趟辛苦你了，這是謝禮</t>
   </si>
@@ -375,29 +374,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
       <charset val="136"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="微軟正黑體 Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -414,25 +420,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -446,38 +452,66 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -524,7 +558,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -823,9 +857,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I69"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="1" customWidth="1"/>
@@ -836,10 +870,11 @@
     <col min="7" max="7" width="16.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
@@ -886,7 +921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="63">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -904,7 +939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
@@ -918,7 +953,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="6" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="63">
       <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
@@ -934,7 +969,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
@@ -952,7 +987,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
@@ -970,7 +1005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
@@ -990,7 +1025,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
@@ -1002,7 +1037,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
@@ -1020,7 +1055,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
@@ -1034,7 +1069,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
@@ -1050,7 +1085,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
@@ -1068,7 +1103,7 @@
       </c>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
@@ -1086,7 +1121,7 @@
       </c>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" s="7" t="s">
         <v>18</v>
       </c>
@@ -1104,7 +1139,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
@@ -1122,7 +1157,7 @@
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9">
       <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
@@ -1138,7 +1173,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="21" ht="94.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="78.75">
       <c r="B21" s="7" t="s">
         <v>16</v>
       </c>
@@ -1156,7 +1191,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9">
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
@@ -1174,7 +1209,7 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9">
       <c r="B23" s="7" t="s">
         <v>18</v>
       </c>
@@ -1192,7 +1227,7 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9">
       <c r="B24" s="7" t="s">
         <v>18</v>
       </c>
@@ -1210,7 +1245,7 @@
       </c>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -1228,7 +1263,7 @@
       </c>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9">
       <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
@@ -1244,7 +1279,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="28" ht="110.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="94.5">
       <c r="B28" s="7" t="s">
         <v>16</v>
       </c>
@@ -1262,7 +1297,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9">
       <c r="B29" s="7" t="s">
         <v>18</v>
       </c>
@@ -1280,7 +1315,7 @@
       </c>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9">
       <c r="B30" s="7" t="s">
         <v>18</v>
       </c>
@@ -1298,7 +1333,7 @@
       </c>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9">
       <c r="B31" s="7" t="s">
         <v>18</v>
       </c>
@@ -1316,7 +1351,7 @@
       </c>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9">
       <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
@@ -1334,7 +1369,7 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9">
       <c r="B33" s="7" t="s">
         <v>18</v>
       </c>
@@ -1350,7 +1385,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="35" ht="110.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="94.5">
       <c r="B35" s="7" t="s">
         <v>16</v>
       </c>
@@ -1368,7 +1403,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9">
       <c r="B36" s="7" t="s">
         <v>18</v>
       </c>
@@ -1386,7 +1421,7 @@
       </c>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9">
       <c r="B37" s="7" t="s">
         <v>18</v>
       </c>
@@ -1404,7 +1439,7 @@
       </c>
       <c r="I37" s="7"/>
     </row>
-    <row r="38" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9">
       <c r="B38" s="7" t="s">
         <v>18</v>
       </c>
@@ -1422,7 +1457,7 @@
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9">
       <c r="B39" s="7" t="s">
         <v>18</v>
       </c>
@@ -1440,7 +1475,7 @@
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9">
       <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
@@ -1456,7 +1491,7 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="42" ht="141.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" ht="110.25">
       <c r="B42" s="7" t="s">
         <v>16</v>
       </c>
@@ -1474,7 +1509,7 @@
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9">
       <c r="B43" s="7" t="s">
         <v>18</v>
       </c>
@@ -1492,7 +1527,7 @@
       </c>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9">
       <c r="B44" s="7" t="s">
         <v>18</v>
       </c>
@@ -1510,7 +1545,7 @@
       </c>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9">
       <c r="B45" s="7" t="s">
         <v>18</v>
       </c>
@@ -1528,7 +1563,7 @@
       </c>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9">
       <c r="B46" s="7" t="s">
         <v>18</v>
       </c>
@@ -1546,7 +1581,7 @@
       </c>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -1562,7 +1597,7 @@
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9">
       <c r="B49" s="7" t="s">
         <v>16</v>
       </c>
@@ -1578,7 +1613,7 @@
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
     </row>
-    <row r="50" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="31.5">
       <c r="B50" s="7" t="s">
         <v>18</v>
       </c>
@@ -1596,7 +1631,7 @@
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9">
       <c r="B51" s="7" t="s">
         <v>18</v>
       </c>
@@ -1612,7 +1647,7 @@
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9">
       <c r="B53" s="7" t="s">
         <v>16</v>
       </c>
@@ -1628,7 +1663,7 @@
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9">
       <c r="B54" s="7" t="s">
         <v>18</v>
       </c>
@@ -1644,7 +1679,7 @@
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="56" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" ht="47.25">
       <c r="B56" s="8" t="s">
         <v>16</v>
       </c>
@@ -1660,7 +1695,7 @@
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9">
       <c r="B57" s="8" t="s">
         <v>18</v>
       </c>
@@ -1678,7 +1713,7 @@
       </c>
       <c r="I57" s="7"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9">
       <c r="B58" s="9" t="s">
         <v>18</v>
       </c>
@@ -1698,7 +1733,7 @@
       </c>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9">
       <c r="B59" s="9" t="s">
         <v>18</v>
       </c>
@@ -1718,7 +1753,7 @@
       </c>
       <c r="I59" s="10"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9">
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
@@ -1728,7 +1763,7 @@
       <c r="H60" s="11"/>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" ht="36.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" ht="31.5">
       <c r="B61" s="12" t="s">
         <v>70</v>
       </c>
@@ -1748,7 +1783,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" ht="33.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" ht="31.5">
       <c r="B62" s="7" t="s">
         <v>16</v>
       </c>
@@ -1764,7 +1799,7 @@
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
     </row>
-    <row r="63" ht="49.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="31.5">
       <c r="B63" s="7" t="s">
         <v>18</v>
       </c>
@@ -1782,7 +1817,7 @@
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
     </row>
-    <row r="65" ht="36" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" ht="31.5">
       <c r="B65" s="12" t="s">
         <v>70</v>
       </c>
@@ -1802,7 +1837,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" ht="57" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" ht="47.25">
       <c r="B66" s="7" t="s">
         <v>16</v>
       </c>
@@ -1818,7 +1853,7 @@
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
     </row>
-    <row r="67" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9">
       <c r="B67" s="7" t="s">
         <v>18</v>
       </c>
@@ -1836,19 +1871,20 @@
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
     </row>
-    <row r="69" ht="31.5" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9">
       <c r="E69" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I70"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
@@ -1859,10 +1895,11 @@
     <col min="7" max="7" width="15.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1891,7 +1928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5">
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1909,7 +1946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="63">
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
@@ -1927,7 +1964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31.5">
       <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
@@ -1941,7 +1978,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="6" ht="78.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="63">
       <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1957,7 +1994,7 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
@@ -1975,7 +2012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1993,7 +2030,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
@@ -2013,7 +2050,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
@@ -2025,7 +2062,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="B11" s="5" t="s">
         <v>18</v>
       </c>
@@ -2043,7 +2080,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
@@ -2057,7 +2094,7 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
@@ -2073,7 +2110,7 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="B15" s="7" t="s">
         <v>18</v>
       </c>
@@ -2091,7 +2128,7 @@
       </c>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2109,7 +2146,7 @@
       </c>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" s="7" t="s">
         <v>18</v>
       </c>
@@ -2127,7 +2164,7 @@
       </c>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
@@ -2145,7 +2182,7 @@
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9">
       <c r="B19" s="7" t="s">
         <v>18</v>
       </c>
@@ -2161,7 +2198,7 @@
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="21" ht="126" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="110.25">
       <c r="B21" s="7" t="s">
         <v>16</v>
       </c>
@@ -2179,7 +2216,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9">
       <c r="B22" s="7" t="s">
         <v>18</v>
       </c>
@@ -2197,7 +2234,7 @@
       </c>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9">
       <c r="B23" s="7" t="s">
         <v>18</v>
       </c>
@@ -2215,7 +2252,7 @@
       </c>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9">
       <c r="B24" s="7" t="s">
         <v>18</v>
       </c>
@@ -2233,7 +2270,7 @@
       </c>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -2251,7 +2288,7 @@
       </c>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9">
       <c r="B26" s="7" t="s">
         <v>18</v>
       </c>
@@ -2267,7 +2304,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="28" ht="141.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="126">
       <c r="B28" s="7" t="s">
         <v>16</v>
       </c>
@@ -2285,7 +2322,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9">
       <c r="B29" s="7" t="s">
         <v>18</v>
       </c>
@@ -2303,7 +2340,7 @@
       </c>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9">
       <c r="B30" s="7" t="s">
         <v>18</v>
       </c>
@@ -2321,7 +2358,7 @@
       </c>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9">
       <c r="B31" s="7" t="s">
         <v>18</v>
       </c>
@@ -2339,7 +2376,7 @@
       </c>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9">
       <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
@@ -2357,7 +2394,7 @@
       </c>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9">
       <c r="B33" s="7" t="s">
         <v>18</v>
       </c>
@@ -2373,7 +2410,7 @@
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="35" ht="157.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="141.75">
       <c r="B35" s="7" t="s">
         <v>16</v>
       </c>
@@ -2391,7 +2428,7 @@
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9">
       <c r="B36" s="7" t="s">
         <v>18</v>
       </c>
@@ -2409,7 +2446,7 @@
       </c>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9">
       <c r="B37" s="7" t="s">
         <v>18</v>
       </c>
@@ -2427,7 +2464,7 @@
       </c>
       <c r="I37" s="7"/>
     </row>
-    <row r="38" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9">
       <c r="B38" s="7" t="s">
         <v>18</v>
       </c>
@@ -2445,7 +2482,7 @@
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9">
       <c r="B39" s="7" t="s">
         <v>18</v>
       </c>
@@ -2463,7 +2500,7 @@
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9">
       <c r="B40" s="7" t="s">
         <v>18</v>
       </c>
@@ -2479,7 +2516,7 @@
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="43" ht="189" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" ht="173.25">
       <c r="B43" s="7" t="s">
         <v>16</v>
       </c>
@@ -2497,7 +2534,7 @@
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9">
       <c r="B44" s="7" t="s">
         <v>18</v>
       </c>
@@ -2515,7 +2552,7 @@
       </c>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9">
       <c r="B45" s="7" t="s">
         <v>18</v>
       </c>
@@ -2533,7 +2570,7 @@
       </c>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9">
       <c r="B46" s="7" t="s">
         <v>18</v>
       </c>
@@ -2551,7 +2588,7 @@
       </c>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2569,7 +2606,7 @@
       </c>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9">
       <c r="B48" s="7" t="s">
         <v>18</v>
       </c>
@@ -2585,7 +2622,7 @@
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
     </row>
-    <row r="50" ht="33.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="31.5">
       <c r="B50" s="12" t="s">
         <v>70</v>
       </c>
@@ -2605,7 +2642,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" ht="31.5">
       <c r="B51" s="7" t="s">
         <v>16</v>
       </c>
@@ -2621,7 +2658,7 @@
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" ht="31.5">
       <c r="B52" s="7" t="s">
         <v>18</v>
       </c>
@@ -2639,7 +2676,7 @@
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
     </row>
-    <row r="54" ht="63" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" ht="47.25">
       <c r="B54" s="7" t="s">
         <v>16</v>
       </c>
@@ -2655,7 +2692,7 @@
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
     </row>
-    <row r="55" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" ht="31.5">
       <c r="B55" s="7" t="s">
         <v>18</v>
       </c>
@@ -2673,7 +2710,7 @@
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9">
       <c r="B56" s="7" t="s">
         <v>18</v>
       </c>
@@ -2689,7 +2726,7 @@
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
     </row>
-    <row r="58" ht="94.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" ht="94.5">
       <c r="B58" s="7" t="s">
         <v>16</v>
       </c>
@@ -2705,7 +2742,7 @@
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9">
       <c r="B59" s="7" t="s">
         <v>18</v>
       </c>
@@ -2723,7 +2760,7 @@
       </c>
       <c r="I59" s="7"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9">
       <c r="B60" s="7" t="s">
         <v>18</v>
       </c>
@@ -2743,7 +2780,7 @@
       </c>
       <c r="I60" s="7"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9">
       <c r="B61" s="7" t="s">
         <v>18</v>
       </c>
@@ -2763,7 +2800,7 @@
       </c>
       <c r="I61" s="7"/>
     </row>
-    <row r="63" ht="94.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="78.75">
       <c r="B63" s="7" t="s">
         <v>16</v>
       </c>
@@ -2779,7 +2816,7 @@
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
     </row>
-    <row r="64" ht="31.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" ht="31.5">
       <c r="B64" s="7" t="s">
         <v>18</v>
       </c>
@@ -2797,7 +2834,7 @@
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9">
       <c r="B65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2813,7 +2850,7 @@
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
     </row>
-    <row r="67" ht="94.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" ht="94.5">
       <c r="B67" s="7" t="s">
         <v>16</v>
       </c>
@@ -2829,7 +2866,7 @@
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9">
       <c r="B68" s="7" t="s">
         <v>18</v>
       </c>
@@ -2847,7 +2884,7 @@
       </c>
       <c r="I68" s="7"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9">
       <c r="B69" s="7" t="s">
         <v>18</v>
       </c>
@@ -2867,7 +2904,7 @@
       </c>
       <c r="I69" s="7"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9">
       <c r="B70" s="7" t="s">
         <v>18</v>
       </c>
@@ -2888,17 +2925,8 @@
       <c r="I70" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>